--- a/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
+++ b/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="517">
   <si>
     <t>Property</t>
   </si>
@@ -376,7 +376,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -840,7 +840,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -955,7 +955,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1005,143 +1005,6 @@
     <t>Condition.subject.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient</t>
-  </si>
-  <si>
-    <t>unidentifiedPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://www.saude.gov.br/fhir/r4/StructureDefinition/BRIndividuoNaoIdentificado-1.0}
-</t>
-  </si>
-  <si>
-    <t>Dados do Indivíduo Não Identificado</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.id</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:gender</t>
-  </si>
-  <si>
-    <t>gender</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:gender.id</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:gender.extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:gender.url</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:gender.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear</t>
-  </si>
-  <si>
-    <t>birthYear</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear.extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear.url</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:reason</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:reason.id</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:reason.extension</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:reason.url</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.extension:reason.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.url</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.url</t>
-  </si>
-  <si>
-    <t>http://www.saude.gov.br/fhir/r4/StructureDefinition/BRIndividuoNaoIdentificado-1.0</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension:unidentifiedPatient.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.subject.extension.value[x]</t>
-  </si>
-  <si>
     <t>Condition.subject.reference</t>
   </si>
   <si>
@@ -1183,7 +1046,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1261,7 +1124,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1346,7 +1209,7 @@
     <t>Condition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1386,7 +1249,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1486,7 +1349,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1575,7 +1438,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1588,7 +1451,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|DiagnosticReport|Observation)
+    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1613,7 +1476,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1659,7 +1522,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1678,7 +1541,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1719,7 +1582,7 @@
     <t>Condition.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -2086,12 +1949,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP99"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.78125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="37.09375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.09375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
@@ -2099,7 +1962,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.2890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2260,7 +2123,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3460,7 +3323,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -3818,7 +3681,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>183</v>
       </c>
@@ -5264,7 +5127,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>270</v>
       </c>
@@ -6828,7 +6691,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>303</v>
       </c>
@@ -7075,7 +6938,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7097,12 +6960,14 @@
         <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>315</v>
+        <v>138</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7175,7 +7040,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7186,14 +7051,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>79</v>
       </c>
@@ -7202,27 +7065,29 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J43" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K43" t="s" s="2">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7271,19 +7136,19 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>182</v>
+        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -7295,7 +7160,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7309,7 +7174,7 @@
         <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7320,7 +7185,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
@@ -7329,25 +7194,27 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>173</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>79</v>
@@ -7365,13 +7232,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7389,7 +7256,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>175</v>
+        <v>329</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7401,7 +7268,7 @@
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -7413,7 +7280,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7424,10 +7291,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7435,10 +7302,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7447,18 +7314,20 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7495,31 +7364,31 @@
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>182</v>
+        <v>334</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7531,7 +7400,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7542,14 +7411,12 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7558,10 +7425,10 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
@@ -7570,13 +7437,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>315</v>
+        <v>173</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>316</v>
+        <v>174</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7627,19 +7494,19 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7651,7 +7518,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7662,21 +7529,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7688,15 +7555,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7733,31 +7602,31 @@
         <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7780,44 +7649,46 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>138</v>
+        <v>339</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>178</v>
+        <v>340</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7841,43 +7712,43 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>182</v>
+        <v>345</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7886,10 +7757,10 @@
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>176</v>
+        <v>346</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7900,10 +7771,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7911,10 +7782,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7923,51 +7794,53 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X49" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="S49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="Y49" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7985,10 +7858,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>92</v>
@@ -7997,7 +7870,7 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -8006,10 +7879,10 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>134</v>
+        <v>346</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -8020,10 +7893,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8031,7 +7904,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>92</v>
@@ -8043,19 +7916,23 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>339</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -8067,7 +7944,7 @@
         <v>79</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>79</v>
@@ -8103,7 +7980,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8124,10 +8001,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>134</v>
+        <v>364</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8138,43 +8015,43 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8187,7 +8064,7 @@
         <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>79</v>
@@ -8223,19 +8100,19 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>182</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8244,10 +8121,10 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8258,10 +8135,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8272,7 +8149,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -8281,16 +8158,16 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>172</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>173</v>
+        <v>375</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>174</v>
+        <v>376</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8341,7 +8218,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>175</v>
+        <v>377</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8353,7 +8230,7 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8362,10 +8239,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>176</v>
+        <v>379</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8376,21 +8253,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8399,19 +8276,19 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>138</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>178</v>
+        <v>383</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>140</v>
+        <v>384</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8449,31 +8326,31 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>182</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8482,10 +8359,10 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8496,10 +8373,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8507,10 +8384,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8519,19 +8396,19 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>333</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>334</v>
+        <v>390</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8539,7 +8416,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>79</v>
@@ -8581,10 +8458,10 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>92</v>
@@ -8593,7 +8470,7 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8616,10 +8493,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8630,7 +8507,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8639,18 +8516,20 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>339</v>
+        <v>394</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8699,7 +8578,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8714,19 +8593,19 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>134</v>
+        <v>400</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
@@ -8734,14 +8613,12 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8750,27 +8627,29 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>315</v>
+        <v>404</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8819,34 +8698,34 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>182</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8854,10 +8733,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>328</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8868,7 +8747,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8880,15 +8759,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>172</v>
+        <v>412</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>173</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8937,7 +8818,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>175</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8946,10 +8827,10 @@
         <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8961,10 +8842,10 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>176</v>
+        <v>417</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8972,21 +8853,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>352</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8995,20 +8876,18 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>138</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9045,31 +8924,31 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>182</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -9078,13 +8957,13 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>176</v>
+        <v>423</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>79</v>
+        <v>424</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -9092,10 +8971,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>353</v>
+        <v>425</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>332</v>
+        <v>425</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9103,10 +8982,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9115,27 +8994,25 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>333</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>79</v>
@@ -9177,10 +9054,10 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>336</v>
+        <v>425</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>92</v>
@@ -9189,7 +9066,7 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
@@ -9201,10 +9078,10 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>134</v>
+        <v>429</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>79</v>
@@ -9212,10 +9089,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>354</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>338</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9226,7 +9103,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9235,16 +9112,16 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>339</v>
+        <v>426</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>340</v>
+        <v>432</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>341</v>
+        <v>433</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9295,7 +9172,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>342</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9316,13 +9193,13 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>79</v>
+        <v>434</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>134</v>
+        <v>435</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>79</v>
+        <v>436</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9330,10 +9207,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>355</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>356</v>
+        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9341,10 +9218,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9356,24 +9233,22 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>438</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>79</v>
@@ -9415,19 +9290,19 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>336</v>
+        <v>437</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9439,7 +9314,7 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>134</v>
+        <v>442</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9450,10 +9325,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>358</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>359</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9476,13 +9351,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>339</v>
+        <v>172</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>340</v>
+        <v>173</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>341</v>
+        <v>174</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9533,7 +9408,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>342</v>
+        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9545,7 +9420,7 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -9557,7 +9432,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9568,21 +9443,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>360</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>360</v>
+        <v>444</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9591,19 +9466,19 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>361</v>
+        <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>362</v>
+        <v>178</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>363</v>
+        <v>140</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9653,19 +9528,19 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>364</v>
+        <v>182</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
@@ -9677,7 +9552,7 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9688,50 +9563,52 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>367</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>79</v>
@@ -9749,13 +9626,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9773,19 +9650,19 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>374</v>
+        <v>449</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
@@ -9808,10 +9685,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9819,7 +9696,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>92</v>
@@ -9831,20 +9708,18 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>376</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9869,13 +9744,13 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>79</v>
+        <v>454</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -9893,7 +9768,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9902,7 +9777,7 @@
         <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>79</v>
+        <v>455</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>103</v>
@@ -9911,13 +9786,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9928,10 +9803,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>381</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>381</v>
+        <v>457</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9942,7 +9817,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9954,13 +9829,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>172</v>
+        <v>458</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>173</v>
+        <v>459</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>174</v>
+        <v>460</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10011,19 +9886,19 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>175</v>
+        <v>457</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>79</v>
+        <v>455</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
@@ -10035,7 +9910,7 @@
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>176</v>
+        <v>461</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10046,21 +9921,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>382</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>382</v>
+        <v>462</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
@@ -10072,17 +9947,15 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>138</v>
+        <v>463</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10107,43 +9980,43 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>79</v>
+        <v>466</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>182</v>
+        <v>462</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
@@ -10155,7 +10028,7 @@
         <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>176</v>
+        <v>467</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -10166,10 +10039,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>468</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10186,26 +10059,24 @@
         <v>79</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>111</v>
+        <v>438</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>384</v>
+        <v>469</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>470</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10229,13 +10100,13 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10253,19 +10124,19 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>390</v>
+        <v>468</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>472</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
@@ -10274,10 +10145,10 @@
         <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10288,10 +10159,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>392</v>
+        <v>474</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>392</v>
+        <v>474</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10302,7 +10173,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -10311,23 +10182,19 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>393</v>
+        <v>173</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10351,13 +10218,13 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>397</v>
+        <v>79</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10375,7 +10242,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>399</v>
+        <v>175</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10387,7 +10254,7 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
@@ -10396,10 +10263,10 @@
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>391</v>
+        <v>176</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10410,21 +10277,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>401</v>
+        <v>475</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>401</v>
+        <v>475</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10433,23 +10300,21 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>402</v>
+        <v>138</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10461,7 +10326,7 @@
         <v>79</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>79</v>
@@ -10497,19 +10362,19 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>407</v>
+        <v>182</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10518,10 +10383,10 @@
         <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>409</v>
+        <v>176</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10532,44 +10397,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10581,7 +10448,7 @@
         <v>79</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>79</v>
@@ -10617,19 +10484,19 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -10638,10 +10505,10 @@
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>134</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10652,10 +10519,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10666,7 +10533,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>79</v>
@@ -10678,13 +10545,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>419</v>
+        <v>158</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>479</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10711,13 +10578,13 @@
         <v>79</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>79</v>
+        <v>480</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -10735,34 +10602,34 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>422</v>
+        <v>477</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>79</v>
+        <v>482</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>423</v>
+        <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>79</v>
@@ -10770,10 +10637,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>486</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>486</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10784,7 +10651,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10796,17 +10663,15 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>487</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10855,16 +10720,16 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>486</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>79</v>
+        <v>482</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>103</v>
@@ -10876,24 +10741,24 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>431</v>
+        <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>490</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>490</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10904,29 +10769,27 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>172</v>
+        <v>491</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>492</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10975,13 +10838,13 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>490</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
@@ -10990,16 +10853,16 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>79</v>
+        <v>494</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>79</v>
+        <v>495</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>134</v>
+        <v>496</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -11010,10 +10873,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>497</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>497</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11024,7 +10887,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>79</v>
@@ -11033,20 +10896,18 @@
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>439</v>
+        <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>440</v>
+        <v>173</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11095,7 +10956,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>175</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11107,22 +10968,22 @@
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>445</v>
+        <v>176</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -11130,21 +10991,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>79</v>
@@ -11153,19 +11014,19 @@
         <v>79</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>448</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>449</v>
+        <v>138</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>450</v>
+        <v>178</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>451</v>
+        <v>140</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11203,46 +11064,46 @@
         <v>79</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>447</v>
+        <v>182</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>453</v>
+        <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>454</v>
+        <v>176</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11250,10 +11111,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>456</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>456</v>
+        <v>499</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11273,19 +11134,19 @@
         <v>79</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>457</v>
+        <v>500</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>459</v>
+        <v>502</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>460</v>
+        <v>503</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11335,7 +11196,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11344,7 +11205,7 @@
         <v>92</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>461</v>
+        <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>103</v>
@@ -11356,13 +11217,13 @@
         <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>79</v>
@@ -11370,10 +11231,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11396,13 +11257,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11453,7 +11314,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>464</v>
+        <v>509</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11474,24 +11335,24 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>467</v>
+        <v>134</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>469</v>
+        <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11499,13 +11360,13 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>79</v>
@@ -11514,13 +11375,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11571,10 +11432,10 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>470</v>
+        <v>515</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>92</v>
@@ -11592,2408 +11453,30 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>474</v>
+        <v>516</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>475</v>
+        <v>79</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP99" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP99">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP79">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
